--- a/examples/schedule_output.xlsx
+++ b/examples/schedule_output.xlsx
@@ -19,7 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -58,11 +61,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,30 +448,35 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>tables_available</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>capacity</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>objective</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>total_shortage</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>total_surplus</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>realized_theo</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>realized_hands</t>
         </is>
@@ -485,21 +494,24 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2" t="n">
         <v>20</v>
       </c>
-      <c r="D2" t="n">
-        <v>14.23</v>
-      </c>
       <c r="E2" t="n">
+        <v>13.93</v>
+      </c>
+      <c r="F2" t="n">
         <v>9</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>29</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>62992</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>12520</v>
       </c>
     </row>
@@ -515,22 +527,58 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D3" t="n">
         <v>18</v>
       </c>
-      <c r="D3" t="n">
-        <v>3.54</v>
-      </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="F3" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="G3" t="n">
-        <v>58712</v>
+        <v>17</v>
       </c>
       <c r="H3" t="n">
-        <v>11944</v>
+        <v>56656</v>
+      </c>
+      <c r="I3" t="n">
+        <v>11752</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>OPTIMAL</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>19</v>
+      </c>
+      <c r="D4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E4" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>35</v>
+      </c>
+      <c r="H4" t="n">
+        <v>57552</v>
+      </c>
+      <c r="I4" t="n">
+        <v>12984</v>
       </c>
     </row>
   </sheetData>
@@ -544,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -575,12 +623,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>has_history</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>rank</t>
+          <t>available_from</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>available_to</t>
         </is>
       </c>
     </row>
@@ -604,11 +657,12 @@
       <c r="E2" t="n">
         <v>32</v>
       </c>
-      <c r="F2" t="n">
-        <v>0.7951</v>
-      </c>
-      <c r="G2" t="n">
-        <v>3</v>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" s="2" t="n">
+        <v>46266</v>
       </c>
     </row>
     <row r="3">
@@ -631,12 +685,11 @@
       <c r="E3" t="n">
         <v>52</v>
       </c>
-      <c r="F3" t="n">
-        <v>0.9302</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -658,12 +711,11 @@
       <c r="E4" t="n">
         <v>39</v>
       </c>
-      <c r="F4" t="n">
-        <v>0.7856</v>
-      </c>
-      <c r="G4" t="n">
-        <v>4</v>
-      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -685,12 +737,11 @@
       <c r="E5" t="n">
         <v>58</v>
       </c>
-      <c r="F5" t="n">
-        <v>0.7782</v>
-      </c>
-      <c r="G5" t="n">
-        <v>5</v>
-      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -712,12 +763,11 @@
       <c r="E6" t="n">
         <v>56</v>
       </c>
-      <c r="F6" t="n">
-        <v>0.6503</v>
-      </c>
-      <c r="G6" t="n">
-        <v>10</v>
-      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -739,12 +789,11 @@
       <c r="E7" t="n">
         <v>52</v>
       </c>
-      <c r="F7" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="G7" t="n">
-        <v>8</v>
-      </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -766,12 +815,11 @@
       <c r="E8" t="n">
         <v>24</v>
       </c>
-      <c r="F8" t="n">
-        <v>0.7655999999999999</v>
-      </c>
-      <c r="G8" t="n">
-        <v>6</v>
-      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -793,12 +841,11 @@
       <c r="E9" t="n">
         <v>48</v>
       </c>
-      <c r="F9" t="n">
-        <v>0.8887</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2</v>
-      </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -820,12 +867,11 @@
       <c r="E10" t="n">
         <v>54</v>
       </c>
-      <c r="F10" t="n">
-        <v>0.6371</v>
-      </c>
-      <c r="G10" t="n">
-        <v>11</v>
-      </c>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -847,12 +893,11 @@
       <c r="E11" t="n">
         <v>56</v>
       </c>
-      <c r="F11" t="n">
-        <v>0.6273</v>
-      </c>
-      <c r="G11" t="n">
-        <v>12</v>
-      </c>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -874,12 +919,11 @@
       <c r="E12" t="n">
         <v>36</v>
       </c>
-      <c r="F12" t="n">
-        <v>0.7027</v>
-      </c>
-      <c r="G12" t="n">
-        <v>9</v>
-      </c>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -901,12 +945,11 @@
       <c r="E13" t="n">
         <v>49</v>
       </c>
-      <c r="F13" t="n">
-        <v>0.744</v>
-      </c>
-      <c r="G13" t="n">
-        <v>7</v>
-      </c>
+      <c r="F13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -928,12 +971,11 @@
       <c r="E14" t="n">
         <v>43</v>
       </c>
-      <c r="F14" t="n">
-        <v>0.4941</v>
-      </c>
-      <c r="G14" t="n">
-        <v>16</v>
-      </c>
+      <c r="F14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -955,12 +997,11 @@
       <c r="E15" t="n">
         <v>45</v>
       </c>
-      <c r="F15" t="n">
-        <v>0.3427</v>
-      </c>
-      <c r="G15" t="n">
-        <v>17</v>
-      </c>
+      <c r="F15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -982,12 +1023,11 @@
       <c r="E16" t="n">
         <v>67</v>
       </c>
-      <c r="F16" t="n">
-        <v>0.5828</v>
-      </c>
-      <c r="G16" t="n">
-        <v>14</v>
-      </c>
+      <c r="F16" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1009,12 +1049,11 @@
       <c r="E17" t="n">
         <v>45</v>
       </c>
-      <c r="F17" t="n">
-        <v>0.5915</v>
-      </c>
-      <c r="G17" t="n">
-        <v>13</v>
-      </c>
+      <c r="F17" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1036,12 +1075,11 @@
       <c r="E18" t="n">
         <v>54</v>
       </c>
-      <c r="F18" t="n">
-        <v>0.1395</v>
-      </c>
-      <c r="G18" t="n">
-        <v>20</v>
-      </c>
+      <c r="F18" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1063,12 +1101,11 @@
       <c r="E19" t="n">
         <v>65</v>
       </c>
-      <c r="F19" t="n">
-        <v>0.5084</v>
-      </c>
-      <c r="G19" t="n">
-        <v>15</v>
-      </c>
+      <c r="F19" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1090,12 +1127,11 @@
       <c r="E20" t="n">
         <v>47</v>
       </c>
-      <c r="F20" t="n">
-        <v>0.2027</v>
-      </c>
-      <c r="G20" t="n">
-        <v>18</v>
-      </c>
+      <c r="F20" t="b">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1111,18 +1147,15 @@
       <c r="C21" t="n">
         <v>0</v>
       </c>
-      <c r="D21" t="n">
-        <v>68</v>
-      </c>
-      <c r="E21" t="n">
-        <v>53</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.1425</v>
-      </c>
-      <c r="G21" t="n">
-        <v>19</v>
-      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1135,7 +1168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1166,15 +1199,20 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>has_history</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>preferred_open_hours</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>shift</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>shift_open_hours</t>
         </is>
@@ -1188,7 +1226,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>T00</t>
+          <t>T01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1197,20 +1235,23 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7951</v>
-      </c>
-      <c r="F2" t="n">
+        <v>0.9302</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
         <v>24</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>24</v>
       </c>
     </row>
@@ -1222,29 +1263,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>T01</t>
+          <t>T07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9302</v>
-      </c>
-      <c r="F3" t="n">
-        <v>24</v>
-      </c>
-      <c r="G3" t="inlineStr">
+        <v>0.8887</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>24</v>
       </c>
     </row>
@@ -1256,7 +1300,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>T02</t>
+          <t>T00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1265,20 +1309,23 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7856</v>
-      </c>
-      <c r="F4" t="n">
+        <v>0.7951</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
         <v>24</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>24</v>
       </c>
     </row>
@@ -1290,7 +1337,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>T03</t>
+          <t>T02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1299,20 +1346,23 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7782</v>
-      </c>
-      <c r="F5" t="n">
+        <v>0.7856</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
         <v>24</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>24</v>
       </c>
     </row>
@@ -1324,30 +1374,33 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>T04</t>
+          <t>T03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6503</v>
-      </c>
-      <c r="F6" t="n">
-        <v>16</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>16</v>
+        <v>0.7782</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>24</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="7">
@@ -1358,7 +1411,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>T05</t>
+          <t>T06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1367,21 +1420,24 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="F7" t="n">
+        <v>0.7655999999999999</v>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
         <v>24</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>16</v>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="8">
@@ -1392,30 +1448,33 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>T06</t>
+          <t>T11</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7655999999999999</v>
-      </c>
-      <c r="F8" t="n">
-        <v>24</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>24</v>
+        <v>0.744</v>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>16</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -1426,7 +1485,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>T07</t>
+          <t>T05</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1435,21 +1494,24 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8887</v>
-      </c>
-      <c r="F9" t="n">
-        <v>16</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
         <v>24</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -1460,7 +1522,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>T08</t>
+          <t>T10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1469,20 +1531,23 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6371</v>
-      </c>
-      <c r="F10" t="n">
-        <v>16</v>
-      </c>
-      <c r="G10" t="inlineStr">
+        <v>0.7027</v>
+      </c>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>16</v>
       </c>
     </row>
@@ -1494,29 +1559,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>T09</t>
+          <t>T04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6273</v>
-      </c>
-      <c r="F11" t="n">
-        <v>16</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
+        <v>0.6503</v>
+      </c>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>16</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>16</v>
       </c>
     </row>
@@ -1528,7 +1596,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>T08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1537,20 +1605,23 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7027</v>
-      </c>
-      <c r="F12" t="n">
-        <v>16</v>
-      </c>
-      <c r="G12" t="inlineStr">
+        <v>0.6371</v>
+      </c>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>16</v>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>16</v>
       </c>
     </row>
@@ -1562,7 +1633,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>T11</t>
+          <t>T09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1571,20 +1642,23 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>0.744</v>
-      </c>
-      <c r="F13" t="n">
-        <v>16</v>
-      </c>
-      <c r="G13" t="inlineStr">
+        <v>0.6273</v>
+      </c>
+      <c r="F13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>16</v>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>16</v>
       </c>
     </row>
@@ -1596,7 +1670,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>T12</t>
+          <t>T15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1605,20 +1679,23 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4941</v>
-      </c>
-      <c r="F14" t="n">
+        <v>0.5915</v>
+      </c>
+      <c r="F14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
         <v>8</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1630,7 +1707,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>T13</t>
+          <t>T14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1639,20 +1716,23 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3427</v>
-      </c>
-      <c r="F15" t="n">
+        <v>0.5828</v>
+      </c>
+      <c r="F15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
         <v>8</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1664,30 +1744,33 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>T14</t>
+          <t>T17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5828</v>
-      </c>
-      <c r="F16" t="n">
+        <v>0.5084</v>
+      </c>
+      <c r="F16" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
         <v>8</v>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>8</v>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1698,7 +1781,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>T15</t>
+          <t>T12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1707,20 +1790,23 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5915</v>
-      </c>
-      <c r="F17" t="n">
+        <v>0.4941</v>
+      </c>
+      <c r="F17" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
         <v>8</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1732,30 +1818,33 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>T16</t>
+          <t>T13</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1395</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
+        <v>0.3427</v>
+      </c>
+      <c r="F18" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>8</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -1766,7 +1855,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>T17</t>
+          <t>T18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1775,20 +1864,23 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5084</v>
-      </c>
-      <c r="F19" t="n">
+        <v>0.2027</v>
+      </c>
+      <c r="F19" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
         <v>8</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1800,7 +1892,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>T18</t>
+          <t>T16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1809,55 +1901,61 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2027</v>
-      </c>
-      <c r="F20" t="n">
-        <v>8</v>
-      </c>
-      <c r="G20" t="inlineStr">
+        <v>0.1395</v>
+      </c>
+      <c r="F20" t="b">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>T19</t>
+          <t>T01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1425</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
+        <v>0.9302</v>
+      </c>
+      <c r="F21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>24</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="22">
@@ -1868,29 +1966,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>T00</t>
+          <t>T07</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7951</v>
-      </c>
-      <c r="F22" t="n">
-        <v>24</v>
-      </c>
-      <c r="G22" t="inlineStr">
+        <v>0.8887</v>
+      </c>
+      <c r="F22" t="b">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>16</v>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>24</v>
       </c>
     </row>
@@ -1902,7 +2003,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>T01</t>
+          <t>T02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1911,20 +2012,23 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9302</v>
-      </c>
-      <c r="F23" t="n">
+        <v>0.7856</v>
+      </c>
+      <c r="F23" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
         <v>24</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>24</v>
       </c>
     </row>
@@ -1936,7 +2040,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>T02</t>
+          <t>T03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1948,17 +2052,20 @@
         <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7856</v>
-      </c>
-      <c r="F24" t="n">
+        <v>0.7782</v>
+      </c>
+      <c r="F24" t="b">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
         <v>24</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>24</v>
       </c>
     </row>
@@ -1970,29 +2077,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>T03</t>
+          <t>T06</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7782</v>
-      </c>
-      <c r="F25" t="n">
+        <v>0.7655999999999999</v>
+      </c>
+      <c r="F25" t="b">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
         <v>24</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>24</v>
       </c>
     </row>
@@ -2004,29 +2114,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>T04</t>
+          <t>T11</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6503</v>
-      </c>
-      <c r="F26" t="n">
-        <v>16</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="F26" t="b">
+        <v>1</v>
+      </c>
+      <c r="G26" t="n">
+        <v>16</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
         <v>16</v>
       </c>
     </row>
@@ -2047,20 +2160,23 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E27" t="n">
         <v>0.735</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27" t="b">
+        <v>1</v>
+      </c>
+      <c r="G27" t="n">
         <v>24</v>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>16</v>
       </c>
     </row>
@@ -2072,29 +2188,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>T06</t>
+          <t>T10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>0.7655999999999999</v>
-      </c>
-      <c r="F28" t="n">
-        <v>24</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
+        <v>0.7027</v>
+      </c>
+      <c r="F28" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>16</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
         <v>16</v>
       </c>
     </row>
@@ -2106,7 +2225,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>T07</t>
+          <t>T04</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2115,20 +2234,23 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8887</v>
-      </c>
-      <c r="F29" t="n">
-        <v>16</v>
-      </c>
-      <c r="G29" t="inlineStr">
+        <v>0.6503</v>
+      </c>
+      <c r="F29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>16</v>
+      </c>
+      <c r="H29" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>16</v>
       </c>
     </row>
@@ -2140,30 +2262,33 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>T08</t>
+          <t>T19</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6371</v>
-      </c>
-      <c r="F30" t="n">
-        <v>16</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H30" t="n">
-        <v>16</v>
+        <v>0.6437</v>
+      </c>
+      <c r="F30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2174,7 +2299,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>T09</t>
+          <t>T08</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2183,20 +2308,23 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E31" t="n">
-        <v>0.6273</v>
-      </c>
-      <c r="F31" t="n">
-        <v>16</v>
-      </c>
-      <c r="G31" t="inlineStr">
+        <v>0.6371</v>
+      </c>
+      <c r="F31" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" t="n">
+        <v>16</v>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>16</v>
       </c>
     </row>
@@ -2208,7 +2336,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>T09</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2217,20 +2345,23 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E32" t="n">
-        <v>0.7027</v>
-      </c>
-      <c r="F32" t="n">
-        <v>16</v>
-      </c>
-      <c r="G32" t="inlineStr">
+        <v>0.6273</v>
+      </c>
+      <c r="F32" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>16</v>
+      </c>
+      <c r="H32" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>16</v>
       </c>
     </row>
@@ -2242,30 +2373,33 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>T11</t>
+          <t>T15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E33" t="n">
-        <v>0.744</v>
-      </c>
-      <c r="F33" t="n">
-        <v>16</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H33" t="n">
-        <v>16</v>
+        <v>0.5915</v>
+      </c>
+      <c r="F33" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" t="n">
+        <v>8</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="34">
@@ -2276,7 +2410,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>T12</t>
+          <t>T14</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2285,20 +2419,23 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E34" t="n">
-        <v>0.4941</v>
-      </c>
-      <c r="F34" t="n">
+        <v>0.5828</v>
+      </c>
+      <c r="F34" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" t="n">
         <v>8</v>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
         <v>8</v>
       </c>
     </row>
@@ -2310,30 +2447,33 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>T13</t>
+          <t>T17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E35" t="n">
-        <v>0.3427</v>
-      </c>
-      <c r="F35" t="n">
+        <v>0.5084</v>
+      </c>
+      <c r="F35" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" t="n">
         <v>8</v>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="H35" t="n">
-        <v>8</v>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2344,7 +2484,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>T14</t>
+          <t>T12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2353,20 +2493,23 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5828</v>
-      </c>
-      <c r="F36" t="n">
+        <v>0.4941</v>
+      </c>
+      <c r="F36" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" t="n">
         <v>8</v>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>8</v>
       </c>
     </row>
@@ -2378,7 +2521,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>T15</t>
+          <t>T13</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2387,20 +2530,23 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E37" t="n">
-        <v>0.5915</v>
-      </c>
-      <c r="F37" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="F37" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" t="n">
         <v>8</v>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
         <v>8</v>
       </c>
     </row>
@@ -2412,7 +2558,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>T16</t>
+          <t>T18</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2421,20 +2567,23 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1395</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="inlineStr">
+        <v>0.2027</v>
+      </c>
+      <c r="F38" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" t="n">
+        <v>8</v>
+      </c>
+      <c r="H38" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="H38" t="n">
+      <c r="I38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2446,7 +2595,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>T17</t>
+          <t>T16</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2455,88 +2604,726 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5084</v>
-      </c>
-      <c r="F39" t="n">
-        <v>8</v>
-      </c>
-      <c r="G39" t="inlineStr">
+        <v>0.1395</v>
+      </c>
+      <c r="F39" t="b">
+        <v>1</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="H39" t="n">
+      <c r="I39" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>T18</t>
+          <t>T01</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>0.2027</v>
-      </c>
-      <c r="F40" t="n">
-        <v>8</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
+        <v>0.9302</v>
+      </c>
+      <c r="F40" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" t="n">
+        <v>24</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>T07</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.8887</v>
+      </c>
+      <c r="F41" t="b">
+        <v>1</v>
+      </c>
+      <c r="G41" t="n">
+        <v>16</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>T02</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7856</v>
+      </c>
+      <c r="F42" t="b">
+        <v>1</v>
+      </c>
+      <c r="G42" t="n">
+        <v>24</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7782</v>
+      </c>
+      <c r="F43" t="b">
+        <v>1</v>
+      </c>
+      <c r="G43" t="n">
+        <v>24</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>5</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.7655999999999999</v>
+      </c>
+      <c r="F44" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" t="n">
+        <v>24</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>T11</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>6</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="F45" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45" t="n">
+        <v>16</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>T05</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>7</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="F46" t="b">
+        <v>1</v>
+      </c>
+      <c r="G46" t="n">
+        <v>24</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>8</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.7027</v>
+      </c>
+      <c r="F47" t="b">
+        <v>1</v>
+      </c>
+      <c r="G47" t="n">
+        <v>16</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>T04</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>9</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.6503</v>
+      </c>
+      <c r="F48" t="b">
+        <v>1</v>
+      </c>
+      <c r="G48" t="n">
+        <v>16</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>T19</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.6437</v>
+      </c>
+      <c r="F49" t="b">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>T08</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.6371</v>
+      </c>
+      <c r="F50" t="b">
+        <v>1</v>
+      </c>
+      <c r="G50" t="n">
+        <v>16</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>T09</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>12</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.6273</v>
+      </c>
+      <c r="F51" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" t="n">
+        <v>16</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>T15</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>13</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.5915</v>
+      </c>
+      <c r="F52" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" t="n">
+        <v>8</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>T14</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>14</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.5828</v>
+      </c>
+      <c r="F53" t="b">
+        <v>1</v>
+      </c>
+      <c r="G53" t="n">
+        <v>8</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>T17</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>15</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.5084</v>
+      </c>
+      <c r="F54" t="b">
+        <v>1</v>
+      </c>
+      <c r="G54" t="n">
+        <v>8</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>16</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.4941</v>
+      </c>
+      <c r="F55" t="b">
+        <v>1</v>
+      </c>
+      <c r="G55" t="n">
+        <v>8</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>T13</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>17</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="F56" t="b">
+        <v>1</v>
+      </c>
+      <c r="G56" t="n">
+        <v>8</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>T18</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>18</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.2027</v>
+      </c>
+      <c r="F57" t="b">
+        <v>1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>8</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>T16</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
         <v>19</v>
       </c>
-      <c r="E41" t="n">
-        <v>0.1425</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" t="inlineStr">
+      <c r="E58" t="n">
+        <v>0.1395</v>
+      </c>
+      <c r="F58" t="b">
+        <v>1</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="H41" t="n">
+      <c r="I58" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2551,7 +3338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3337,13 +4124,13 @@
         <v>18</v>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -3367,13 +4154,13 @@
         <v>18</v>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -3397,13 +4184,13 @@
         <v>18</v>
       </c>
       <c r="F28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -3427,13 +4214,13 @@
         <v>18</v>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -3457,10 +4244,10 @@
         <v>18</v>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -3487,13 +4274,13 @@
         <v>18</v>
       </c>
       <c r="F31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -3517,10 +4304,10 @@
         <v>18</v>
       </c>
       <c r="F32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -3547,10 +4334,10 @@
         <v>18</v>
       </c>
       <c r="F33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -3577,13 +4364,13 @@
         <v>18</v>
       </c>
       <c r="F34" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -3607,13 +4394,13 @@
         <v>18</v>
       </c>
       <c r="F35" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -3637,10 +4424,10 @@
         <v>18</v>
       </c>
       <c r="F36" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -3667,13 +4454,13 @@
         <v>18</v>
       </c>
       <c r="F37" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -3697,13 +4484,13 @@
         <v>18</v>
       </c>
       <c r="F38" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -3727,13 +4514,13 @@
         <v>18</v>
       </c>
       <c r="F39" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -3757,13 +4544,13 @@
         <v>18</v>
       </c>
       <c r="F40" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -3787,10 +4574,10 @@
         <v>18</v>
       </c>
       <c r="F41" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -3817,10 +4604,10 @@
         <v>18</v>
       </c>
       <c r="F42" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -3847,13 +4634,13 @@
         <v>18</v>
       </c>
       <c r="F43" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -3877,13 +4664,13 @@
         <v>18</v>
       </c>
       <c r="F44" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -3907,13 +4694,13 @@
         <v>18</v>
       </c>
       <c r="F45" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3937,13 +4724,13 @@
         <v>18</v>
       </c>
       <c r="F46" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3967,10 +4754,10 @@
         <v>18</v>
       </c>
       <c r="F47" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -3997,13 +4784,13 @@
         <v>18</v>
       </c>
       <c r="F48" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -4027,13 +4814,733 @@
         <v>18</v>
       </c>
       <c r="F49" t="n">
+        <v>7</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>4</v>
+      </c>
+      <c r="E50" t="n">
+        <v>20</v>
+      </c>
+      <c r="F50" t="n">
+        <v>6</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>4</v>
+      </c>
+      <c r="E51" t="n">
+        <v>20</v>
+      </c>
+      <c r="F51" t="n">
+        <v>6</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>2</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>4</v>
+      </c>
+      <c r="E52" t="n">
+        <v>20</v>
+      </c>
+      <c r="F52" t="n">
+        <v>6</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>3</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>5</v>
+      </c>
+      <c r="E53" t="n">
+        <v>20</v>
+      </c>
+      <c r="F53" t="n">
+        <v>6</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>4</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>6</v>
+      </c>
+      <c r="E54" t="n">
+        <v>20</v>
+      </c>
+      <c r="F54" t="n">
+        <v>6</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>5</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>9</v>
+      </c>
+      <c r="E55" t="n">
+        <v>20</v>
+      </c>
+      <c r="F55" t="n">
+        <v>10</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>6</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" t="n">
+        <v>20</v>
+      </c>
+      <c r="F56" t="n">
+        <v>10</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>7</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>11</v>
+      </c>
+      <c r="E57" t="n">
+        <v>20</v>
+      </c>
+      <c r="F57" t="n">
+        <v>10</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
         <v>8</v>
       </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>12</v>
+      </c>
+      <c r="E58" t="n">
+        <v>20</v>
+      </c>
+      <c r="F58" t="n">
+        <v>13</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>9</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>11</v>
+      </c>
+      <c r="E59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F59" t="n">
+        <v>13</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>10</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>12</v>
+      </c>
+      <c r="E60" t="n">
+        <v>20</v>
+      </c>
+      <c r="F60" t="n">
+        <v>13</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>11</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10</v>
+      </c>
+      <c r="E61" t="n">
+        <v>20</v>
+      </c>
+      <c r="F61" t="n">
+        <v>13</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>12</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>11</v>
+      </c>
+      <c r="E62" t="n">
+        <v>20</v>
+      </c>
+      <c r="F62" t="n">
+        <v>13</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>13</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>13</v>
+      </c>
+      <c r="E63" t="n">
+        <v>20</v>
+      </c>
+      <c r="F63" t="n">
+        <v>17</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>14</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>16</v>
+      </c>
+      <c r="E64" t="n">
+        <v>20</v>
+      </c>
+      <c r="F64" t="n">
+        <v>17</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>15</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>18</v>
+      </c>
+      <c r="E65" t="n">
+        <v>20</v>
+      </c>
+      <c r="F65" t="n">
+        <v>17</v>
+      </c>
+      <c r="G65" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>16</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>17</v>
+      </c>
+      <c r="E66" t="n">
+        <v>20</v>
+      </c>
+      <c r="F66" t="n">
+        <v>17</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>17</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>16</v>
+      </c>
+      <c r="E67" t="n">
+        <v>20</v>
+      </c>
+      <c r="F67" t="n">
+        <v>17</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>18</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>15</v>
+      </c>
+      <c r="E68" t="n">
+        <v>20</v>
+      </c>
+      <c r="F68" t="n">
+        <v>17</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>19</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>16</v>
+      </c>
+      <c r="E69" t="n">
+        <v>20</v>
+      </c>
+      <c r="F69" t="n">
+        <v>17</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>20</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>14</v>
+      </c>
+      <c r="E70" t="n">
+        <v>20</v>
+      </c>
+      <c r="F70" t="n">
+        <v>17</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>21</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>11</v>
+      </c>
+      <c r="E71" t="n">
+        <v>20</v>
+      </c>
+      <c r="F71" t="n">
+        <v>9</v>
+      </c>
+      <c r="G71" t="n">
+        <v>2</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>22</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>7</v>
+      </c>
+      <c r="E72" t="n">
+        <v>20</v>
+      </c>
+      <c r="F72" t="n">
+        <v>9</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>23</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>5</v>
+      </c>
+      <c r="E73" t="n">
+        <v>20</v>
+      </c>
+      <c r="F73" t="n">
+        <v>9</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/examples/schedule_output.xlsx
+++ b/examples/schedule_output.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fleet" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="schedules" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="coverage" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="fleet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="schedules" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="coverage" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,16 +23,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -43,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -51,21 +48,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -436,47 +424,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>day</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>tables_available</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>capacity</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>objective</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>total_shortage</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>total_surplus</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>realized_theo</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>realized_hands</t>
         </is>
@@ -596,42 +584,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>table</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>pod</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>preferred_open_hours</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>theo_per_open_hour</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>patron_hands_per_hour</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>has_history</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>available_from</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>available_to</t>
         </is>
@@ -661,7 +649,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="1" t="n">
         <v>46266</v>
       </c>
     </row>
@@ -1152,7 +1140,7 @@
       <c r="F21" t="b">
         <v>0</v>
       </c>
-      <c r="G21" s="2" t="n">
+      <c r="G21" s="1" t="n">
         <v>46267</v>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -1172,47 +1160,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>day</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>table</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pod</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>has_history</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>preferred_open_hours</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>shift</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>shift_open_hours</t>
         </is>
@@ -3342,42 +3330,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>day</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>hour_index</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>clock</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>demand</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>capacity</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>tables_open</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>shortage</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>surplus</t>
         </is>

--- a/examples/schedule_output.xlsx
+++ b/examples/schedule_output.xlsx
@@ -488,7 +488,7 @@
         <v>20</v>
       </c>
       <c r="E2" t="n">
-        <v>13.93</v>
+        <v>13.63</v>
       </c>
       <c r="F2" t="n">
         <v>9</v>
@@ -521,7 +521,7 @@
         <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2</v>
+        <v>3.97</v>
       </c>
       <c r="F3" t="n">
         <v>8</v>
@@ -554,19 +554,19 @@
         <v>20</v>
       </c>
       <c r="E4" t="n">
-        <v>8.210000000000001</v>
+        <v>7.95</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H4" t="n">
-        <v>57552</v>
+        <v>56152</v>
       </c>
       <c r="I4" t="n">
-        <v>12984</v>
+        <v>13352</v>
       </c>
     </row>
   </sheetData>
@@ -1156,7 +1156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1205,6 +1205,11 @@
           <t>shift_open_hours</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>window_desirability</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1242,6 +1247,9 @@
       <c r="I2" t="n">
         <v>24</v>
       </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1279,6 +1287,9 @@
       <c r="I3" t="n">
         <v>24</v>
       </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1316,6 +1327,9 @@
       <c r="I4" t="n">
         <v>24</v>
       </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1353,6 +1367,9 @@
       <c r="I5" t="n">
         <v>24</v>
       </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1390,6 +1407,9 @@
       <c r="I6" t="n">
         <v>24</v>
       </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1427,6 +1447,9 @@
       <c r="I7" t="n">
         <v>24</v>
       </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1464,6 +1487,9 @@
       <c r="I8" t="n">
         <v>16</v>
       </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1495,11 +1521,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>16</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1538,6 +1567,9 @@
       <c r="I10" t="n">
         <v>16</v>
       </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1569,11 +1601,14 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>16</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1612,6 +1647,9 @@
       <c r="I12" t="n">
         <v>16</v>
       </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1649,6 +1687,9 @@
       <c r="I13" t="n">
         <v>16</v>
       </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1686,6 +1727,9 @@
       <c r="I14" t="n">
         <v>8</v>
       </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1723,6 +1767,9 @@
       <c r="I15" t="n">
         <v>8</v>
       </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1760,6 +1807,9 @@
       <c r="I16" t="n">
         <v>0</v>
       </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1847,9 @@
       <c r="I17" t="n">
         <v>8</v>
       </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1834,6 +1887,9 @@
       <c r="I18" t="n">
         <v>8</v>
       </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1871,6 +1927,9 @@
       <c r="I19" t="n">
         <v>0</v>
       </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1908,6 +1967,9 @@
       <c r="I20" t="n">
         <v>0</v>
       </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1945,6 +2007,9 @@
       <c r="I21" t="n">
         <v>24</v>
       </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1982,6 +2047,9 @@
       <c r="I22" t="n">
         <v>24</v>
       </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2019,6 +2087,9 @@
       <c r="I23" t="n">
         <v>24</v>
       </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2056,6 +2127,9 @@
       <c r="I24" t="n">
         <v>24</v>
       </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2093,6 +2167,9 @@
       <c r="I25" t="n">
         <v>24</v>
       </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2130,6 +2207,9 @@
       <c r="I26" t="n">
         <v>16</v>
       </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2167,6 +2247,9 @@
       <c r="I27" t="n">
         <v>16</v>
       </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2204,6 +2287,9 @@
       <c r="I28" t="n">
         <v>16</v>
       </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2241,6 +2327,9 @@
       <c r="I29" t="n">
         <v>16</v>
       </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2278,6 +2367,9 @@
       <c r="I30" t="n">
         <v>0</v>
       </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2315,6 +2407,9 @@
       <c r="I31" t="n">
         <v>16</v>
       </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2352,6 +2447,9 @@
       <c r="I32" t="n">
         <v>16</v>
       </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2389,6 +2487,9 @@
       <c r="I33" t="n">
         <v>8</v>
       </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2426,6 +2527,9 @@
       <c r="I34" t="n">
         <v>8</v>
       </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2463,6 +2567,9 @@
       <c r="I35" t="n">
         <v>0</v>
       </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2500,6 +2607,9 @@
       <c r="I36" t="n">
         <v>8</v>
       </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2537,6 +2647,9 @@
       <c r="I37" t="n">
         <v>8</v>
       </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2574,6 +2687,9 @@
       <c r="I38" t="n">
         <v>0</v>
       </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2611,6 +2727,9 @@
       <c r="I39" t="n">
         <v>0</v>
       </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2642,11 +2761,14 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>16</v>
+        <v>8</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.3846</v>
       </c>
     </row>
     <row r="41">
@@ -2685,6 +2807,9 @@
       <c r="I41" t="n">
         <v>24</v>
       </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2716,11 +2841,14 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>16</v>
+        <v>8</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.3846</v>
       </c>
     </row>
     <row r="43">
@@ -2753,11 +2881,14 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>16</v>
+        <v>8</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.3846</v>
       </c>
     </row>
     <row r="44">
@@ -2796,6 +2927,9 @@
       <c r="I44" t="n">
         <v>24</v>
       </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2833,6 +2967,9 @@
       <c r="I45" t="n">
         <v>16</v>
       </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2870,6 +3007,9 @@
       <c r="I46" t="n">
         <v>24</v>
       </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2907,6 +3047,9 @@
       <c r="I47" t="n">
         <v>16</v>
       </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2944,6 +3087,9 @@
       <c r="I48" t="n">
         <v>24</v>
       </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2975,11 +3121,14 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>24</v>
+        <v>8</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3018,6 +3167,9 @@
       <c r="I50" t="n">
         <v>16</v>
       </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3055,6 +3207,9 @@
       <c r="I51" t="n">
         <v>16</v>
       </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3086,11 +3241,14 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>8</v>
+        <v>24</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3123,11 +3281,14 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>8</v>
+        <v>24</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3160,11 +3321,14 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>24</v>
+        <v>8</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3197,12 +3361,15 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>J</t>
         </is>
       </c>
       <c r="I55" t="n">
         <v>8</v>
       </c>
+      <c r="J55" t="n">
+        <v>0.4359</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3234,12 +3401,15 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>J</t>
         </is>
       </c>
       <c r="I56" t="n">
         <v>8</v>
       </c>
+      <c r="J56" t="n">
+        <v>0.4359</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3271,11 +3441,14 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3308,11 +3481,14 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3542,13 +3718,13 @@
         <v>20</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -3572,13 +3748,13 @@
         <v>20</v>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -3602,10 +3778,10 @@
         <v>20</v>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4022,10 +4198,10 @@
         <v>20</v>
       </c>
       <c r="F23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -4052,13 +4228,13 @@
         <v>20</v>
       </c>
       <c r="F24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -4082,13 +4258,13 @@
         <v>20</v>
       </c>
       <c r="F25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -5072,13 +5248,13 @@
         <v>20</v>
       </c>
       <c r="F58" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -5102,13 +5278,13 @@
         <v>20</v>
       </c>
       <c r="F59" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -5132,13 +5308,13 @@
         <v>20</v>
       </c>
       <c r="F60" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -5162,13 +5338,13 @@
         <v>20</v>
       </c>
       <c r="F61" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -5192,13 +5368,13 @@
         <v>20</v>
       </c>
       <c r="F62" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -5222,13 +5398,13 @@
         <v>20</v>
       </c>
       <c r="F63" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -5252,13 +5428,13 @@
         <v>20</v>
       </c>
       <c r="F64" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -5282,10 +5458,10 @@
         <v>20</v>
       </c>
       <c r="F65" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>

--- a/examples/schedule_output.xlsx
+++ b/examples/schedule_output.xlsx
@@ -488,7 +488,7 @@
         <v>20</v>
       </c>
       <c r="E2" t="n">
-        <v>13.63</v>
+        <v>11.7</v>
       </c>
       <c r="F2" t="n">
         <v>9</v>
@@ -521,7 +521,7 @@
         <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>3.97</v>
+        <v>1.97</v>
       </c>
       <c r="F3" t="n">
         <v>8</v>
@@ -554,7 +554,7 @@
         <v>20</v>
       </c>
       <c r="E4" t="n">
-        <v>7.95</v>
+        <v>4.97</v>
       </c>
       <c r="F4" t="n">
         <v>5</v>
@@ -563,10 +563,10 @@
         <v>28</v>
       </c>
       <c r="H4" t="n">
-        <v>56152</v>
+        <v>58824</v>
       </c>
       <c r="I4" t="n">
-        <v>13352</v>
+        <v>13016</v>
       </c>
     </row>
   </sheetData>
@@ -1156,7 +1156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:K58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1210,6 +1210,11 @@
           <t>window_desirability</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>pod_split_soft</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1250,6 +1255,9 @@
       <c r="J2" t="n">
         <v>0</v>
       </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1290,6 +1298,9 @@
       <c r="J3" t="n">
         <v>0</v>
       </c>
+      <c r="K3" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1330,6 +1341,9 @@
       <c r="J4" t="n">
         <v>0</v>
       </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1370,6 +1384,9 @@
       <c r="J5" t="n">
         <v>0</v>
       </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1410,6 +1427,9 @@
       <c r="J6" t="n">
         <v>0</v>
       </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1450,6 +1470,9 @@
       <c r="J7" t="n">
         <v>0</v>
       </c>
+      <c r="K7" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1490,6 +1513,9 @@
       <c r="J8" t="n">
         <v>1</v>
       </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1521,13 +1547,16 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>16</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1570,6 +1599,9 @@
       <c r="J10" t="n">
         <v>1</v>
       </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1601,13 +1633,16 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>16</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1650,6 +1685,9 @@
       <c r="J12" t="n">
         <v>1</v>
       </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1690,6 +1728,9 @@
       <c r="J13" t="n">
         <v>1</v>
       </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1730,6 +1771,9 @@
       <c r="J14" t="n">
         <v>1</v>
       </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1770,6 +1814,9 @@
       <c r="J15" t="n">
         <v>1</v>
       </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1810,6 +1857,9 @@
       <c r="J16" t="n">
         <v>0</v>
       </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1850,6 +1900,9 @@
       <c r="J17" t="n">
         <v>1</v>
       </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1890,6 +1943,9 @@
       <c r="J18" t="n">
         <v>1</v>
       </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1930,6 +1986,9 @@
       <c r="J19" t="n">
         <v>0</v>
       </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1970,6 +2029,9 @@
       <c r="J20" t="n">
         <v>0</v>
       </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2010,6 +2072,9 @@
       <c r="J21" t="n">
         <v>0</v>
       </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2050,6 +2115,9 @@
       <c r="J22" t="n">
         <v>0</v>
       </c>
+      <c r="K22" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2090,6 +2158,9 @@
       <c r="J23" t="n">
         <v>0</v>
       </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2130,6 +2201,9 @@
       <c r="J24" t="n">
         <v>0</v>
       </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2170,6 +2244,9 @@
       <c r="J25" t="n">
         <v>0</v>
       </c>
+      <c r="K25" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2210,6 +2287,9 @@
       <c r="J26" t="n">
         <v>1</v>
       </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2250,6 +2330,9 @@
       <c r="J27" t="n">
         <v>0</v>
       </c>
+      <c r="K27" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2290,6 +2373,9 @@
       <c r="J28" t="n">
         <v>1</v>
       </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2330,6 +2416,9 @@
       <c r="J29" t="n">
         <v>0</v>
       </c>
+      <c r="K29" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2370,6 +2459,9 @@
       <c r="J30" t="n">
         <v>0</v>
       </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2410,6 +2502,9 @@
       <c r="J31" t="n">
         <v>1</v>
       </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2450,6 +2545,9 @@
       <c r="J32" t="n">
         <v>1</v>
       </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2490,6 +2588,9 @@
       <c r="J33" t="n">
         <v>1</v>
       </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2530,6 +2631,9 @@
       <c r="J34" t="n">
         <v>1</v>
       </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2570,6 +2674,9 @@
       <c r="J35" t="n">
         <v>0</v>
       </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2610,6 +2717,9 @@
       <c r="J36" t="n">
         <v>1</v>
       </c>
+      <c r="K36" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2650,6 +2760,9 @@
       <c r="J37" t="n">
         <v>1</v>
       </c>
+      <c r="K37" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2690,6 +2803,9 @@
       <c r="J38" t="n">
         <v>0</v>
       </c>
+      <c r="K38" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2730,6 +2846,9 @@
       <c r="J39" t="n">
         <v>0</v>
       </c>
+      <c r="K39" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2761,14 +2880,17 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>0.3846</v>
+        <v>0</v>
+      </c>
+      <c r="K40" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2810,6 +2932,9 @@
       <c r="J41" t="n">
         <v>0</v>
       </c>
+      <c r="K41" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2841,14 +2966,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>0.3846</v>
+        <v>0</v>
+      </c>
+      <c r="K42" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2890,6 +3018,9 @@
       <c r="J43" t="n">
         <v>0.3846</v>
       </c>
+      <c r="K43" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2930,6 +3061,9 @@
       <c r="J44" t="n">
         <v>0</v>
       </c>
+      <c r="K44" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2970,6 +3104,9 @@
       <c r="J45" t="n">
         <v>1</v>
       </c>
+      <c r="K45" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3010,6 +3147,9 @@
       <c r="J46" t="n">
         <v>0</v>
       </c>
+      <c r="K46" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3050,6 +3190,9 @@
       <c r="J47" t="n">
         <v>1</v>
       </c>
+      <c r="K47" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3090,6 +3233,9 @@
       <c r="J48" t="n">
         <v>0</v>
       </c>
+      <c r="K48" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3121,13 +3267,16 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>J</t>
         </is>
       </c>
       <c r="I49" t="n">
         <v>8</v>
       </c>
       <c r="J49" t="n">
+        <v>0.4359</v>
+      </c>
+      <c r="K49" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3170,6 +3319,9 @@
       <c r="J50" t="n">
         <v>1</v>
       </c>
+      <c r="K50" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3210,6 +3362,9 @@
       <c r="J51" t="n">
         <v>1</v>
       </c>
+      <c r="K51" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3241,13 +3396,16 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="J52" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3281,13 +3439,16 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="J53" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3321,13 +3482,16 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>J</t>
         </is>
       </c>
       <c r="I54" t="n">
         <v>8</v>
       </c>
       <c r="J54" t="n">
+        <v>0.4359</v>
+      </c>
+      <c r="K54" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3361,14 +3525,17 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I55" t="n">
         <v>8</v>
       </c>
       <c r="J55" t="n">
-        <v>0.4359</v>
+        <v>1</v>
+      </c>
+      <c r="K55" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3401,14 +3568,17 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I56" t="n">
         <v>8</v>
       </c>
       <c r="J56" t="n">
-        <v>0.4359</v>
+        <v>1</v>
+      </c>
+      <c r="K56" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3441,13 +3611,16 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I57" t="n">
         <v>8</v>
       </c>
       <c r="J57" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="K57" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3481,13 +3654,16 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I58" t="n">
         <v>8</v>
       </c>
       <c r="J58" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="K58" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3718,13 +3894,13 @@
         <v>20</v>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3748,13 +3924,13 @@
         <v>20</v>
       </c>
       <c r="F8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -3778,10 +3954,10 @@
         <v>20</v>
       </c>
       <c r="F9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4198,10 +4374,10 @@
         <v>20</v>
       </c>
       <c r="F23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -4228,13 +4404,13 @@
         <v>20</v>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -4258,13 +4434,13 @@
         <v>20</v>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">

--- a/examples/schedule_output.xlsx
+++ b/examples/schedule_output.xlsx
@@ -488,19 +488,19 @@
         <v>20</v>
       </c>
       <c r="E2" t="n">
-        <v>11.7</v>
+        <v>9.48</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H2" t="n">
-        <v>62992</v>
+        <v>64184</v>
       </c>
       <c r="I2" t="n">
-        <v>12520</v>
+        <v>13040</v>
       </c>
     </row>
     <row r="3">
@@ -521,7 +521,7 @@
         <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>1.97</v>
+        <v>-0.49</v>
       </c>
       <c r="F3" t="n">
         <v>8</v>
@@ -530,10 +530,10 @@
         <v>17</v>
       </c>
       <c r="H3" t="n">
-        <v>56656</v>
+        <v>55432</v>
       </c>
       <c r="I3" t="n">
-        <v>11752</v>
+        <v>11568</v>
       </c>
     </row>
     <row r="4">
@@ -554,7 +554,7 @@
         <v>20</v>
       </c>
       <c r="E4" t="n">
-        <v>4.97</v>
+        <v>-0.48</v>
       </c>
       <c r="F4" t="n">
         <v>5</v>
@@ -563,10 +563,10 @@
         <v>28</v>
       </c>
       <c r="H4" t="n">
-        <v>58824</v>
+        <v>60456</v>
       </c>
       <c r="I4" t="n">
-        <v>13016</v>
+        <v>13104</v>
       </c>
     </row>
   </sheetData>
@@ -1299,7 +1299,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1471,7 +1471,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1547,17 +1547,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>16</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1633,17 +1633,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>16</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1848,14 +1848,14 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="b">
         <v>0</v>
@@ -2116,7 +2116,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2245,7 +2245,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2321,17 +2321,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I27" t="n">
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2407,17 +2407,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I29" t="n">
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2450,14 +2450,14 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="b">
         <v>0</v>
@@ -2493,14 +2493,14 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="I31" t="n">
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="b">
         <v>0</v>
@@ -2536,14 +2536,14 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="I32" t="n">
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="b">
         <v>0</v>
@@ -2665,14 +2665,14 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="b">
         <v>0</v>
@@ -2708,14 +2708,14 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" t="b">
         <v>0</v>
@@ -2751,14 +2751,14 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="b">
         <v>0</v>
@@ -2890,7 +2890,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2976,7 +2976,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -3009,17 +3009,17 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I43" t="n">
         <v>8</v>
       </c>
       <c r="J43" t="n">
-        <v>0.3846</v>
+        <v>1</v>
       </c>
       <c r="K43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -3267,17 +3267,17 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I49" t="n">
         <v>8</v>
       </c>
       <c r="J49" t="n">
-        <v>0.4359</v>
+        <v>1</v>
       </c>
       <c r="K49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3396,14 +3396,14 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52" t="b">
         <v>0</v>
@@ -3439,14 +3439,14 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K53" t="b">
         <v>0</v>
@@ -3482,17 +3482,17 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I54" t="n">
         <v>8</v>
       </c>
       <c r="J54" t="n">
-        <v>0.4359</v>
+        <v>1</v>
       </c>
       <c r="K54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3611,17 +3611,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>0.3846</v>
+        <v>0</v>
       </c>
       <c r="K57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3654,17 +3654,17 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0.3846</v>
+        <v>0</v>
       </c>
       <c r="K58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3894,13 +3894,13 @@
         <v>20</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -3924,13 +3924,13 @@
         <v>20</v>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -3954,10 +3954,10 @@
         <v>20</v>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4134,13 +4134,13 @@
         <v>20</v>
       </c>
       <c r="F15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -4164,13 +4164,13 @@
         <v>20</v>
       </c>
       <c r="F16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -4194,10 +4194,10 @@
         <v>20</v>
       </c>
       <c r="F17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -4224,13 +4224,13 @@
         <v>20</v>
       </c>
       <c r="F18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -4254,13 +4254,13 @@
         <v>20</v>
       </c>
       <c r="F19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -4284,13 +4284,13 @@
         <v>20</v>
       </c>
       <c r="F20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -4314,10 +4314,10 @@
         <v>20</v>
       </c>
       <c r="F21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -4344,13 +4344,13 @@
         <v>20</v>
       </c>
       <c r="F22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -4374,10 +4374,10 @@
         <v>20</v>
       </c>
       <c r="F23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -4404,13 +4404,13 @@
         <v>20</v>
       </c>
       <c r="F24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -4434,13 +4434,13 @@
         <v>20</v>
       </c>
       <c r="F25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -5574,13 +5574,13 @@
         <v>20</v>
       </c>
       <c r="F63" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
@@ -5604,13 +5604,13 @@
         <v>20</v>
       </c>
       <c r="F64" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -5634,10 +5634,10 @@
         <v>20</v>
       </c>
       <c r="F65" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -5814,10 +5814,10 @@
         <v>20</v>
       </c>
       <c r="F71" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -5844,13 +5844,13 @@
         <v>20</v>
       </c>
       <c r="F72" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -5874,13 +5874,13 @@
         <v>20</v>
       </c>
       <c r="F73" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
